--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_26-10-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_26-10-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D582E9-E03E-42EF-88F3-AC515A4F83F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="32880" yWindow="2310" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="271">
   <si>
     <t>SKU</t>
   </si>
@@ -280,60 +286,9 @@
     <t>£791.80</t>
   </si>
   <si>
-    <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes.json</t>
-  </si>
-  <si>
-    <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes.json</t>
-  </si>
-  <si>
     <t>N/L</t>
   </si>
   <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-25mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-30mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-40mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-50mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-60mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-70mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-75mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-80mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-90mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-100mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-110mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-120mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-130mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-140mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-150mm.html</t>
-  </si>
-  <si>
     <t>£13.77</t>
   </si>
   <si>
@@ -487,37 +442,6 @@
     <t>£62.09</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (457, 837). Other element would receive the click: &lt;button type="button" class="btn btn-primary gap-2" data-role="cta"&gt;...&lt;/button&gt;
-  (Session info: chrome=156.0.8078.47); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff7951d3f45]
-	(No symbol) [0x7ff7950d4f90]
-	(No symbol) [0x7ff794f52c53]
-	(No symbol) [0x7ff7957ab1c2]
-	(No symbol) [0x7ff7957a97e3]
-	(No symbol) [0x7ff7957a7737]
-	(No symbol) [0x7ff7957a6ebe]
-	(No symbol) [0x7ff79579baea]
-	(No symbol) [0x7ff7957b81ca]
-	(No symbol) [0x7ff79579b529]
-	(No symbol) [0x7ff79579b4c0]
-	(No symbol) [0x7ff794f825d1]
-	(No symbol) [0x7ff794f67cb9]
-	(No symbol) [0x7ff794f68ff3]
-	(No symbol) [0x7ff79568e1a1]
-	(No symbol) [0x7ff7956b181b]
-	(No symbol) [0x7ff7956a7ece]
-	(No symbol) [0x7ff7952fb10e]
-	(No symbol) [0x7ff7950e3db5]
-	(No symbol) [0x7ff7950de694]
-	(No symbol) [0x7ff7950de824]
-	(No symbol) [0x7ff7950c6bdc]
-	(No symbol) [0x7ff8df39dda7]
-	(No symbol) [0x7ff8e021ee4c]
-</t>
-  </si>
-  <si>
     <t>£17.64</t>
   </si>
   <si>
@@ -557,12 +481,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£117.75</t>
-  </si>
-  <si>
-    <t>£119.36</t>
-  </si>
-  <si>
     <t>£566.26</t>
   </si>
   <si>
@@ -617,51 +535,12 @@
     <t>£23.13</t>
   </si>
   <si>
-    <t>£19.27</t>
-  </si>
-  <si>
-    <t>£20.83</t>
-  </si>
-  <si>
-    <t>£24.26</t>
-  </si>
-  <si>
-    <t>£27.59</t>
-  </si>
-  <si>
-    <t>£31.06</t>
-  </si>
-  <si>
-    <t>£40.83</t>
-  </si>
-  <si>
-    <t>£43.06</t>
-  </si>
-  <si>
-    <t>£55.70</t>
-  </si>
-  <si>
-    <t>£74.88</t>
-  </si>
-  <si>
-    <t>£66.58</t>
-  </si>
-  <si>
-    <t>£78.08</t>
-  </si>
-  <si>
     <t>£126.96</t>
   </si>
   <si>
     <t>£122.43</t>
   </si>
   <si>
-    <t>£463.00</t>
-  </si>
-  <si>
-    <t>£370.40</t>
-  </si>
-  <si>
     <t>£13.90</t>
   </si>
   <si>
@@ -755,26 +634,212 @@
     <t>£57.66</t>
   </si>
   <si>
-    <t>Error: 404 Client Error: Not Found for url: https://diybuildingsupplies.co.uk/products/50mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 404 Client Error: Not Found for url: https://diybuildingsupplies.co.uk/products/100mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 404 Client Error: Not Found for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/90mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
-  </si>
-  <si>
-    <t>Error: 404 Client Error: Not Found for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/115mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
-  </si>
-  <si>
-    <t>Error: 404 Client Error: Not Found for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/140mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
+    <t>£13.75</t>
+  </si>
+  <si>
+    <t>£16.50</t>
+  </si>
+  <si>
+    <t>£21.00</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£29.00</t>
+  </si>
+  <si>
+    <t>£28.75</t>
+  </si>
+  <si>
+    <t>£32.00</t>
+  </si>
+  <si>
+    <t>£35.50</t>
+  </si>
+  <si>
+    <t>£35.00</t>
+  </si>
+  <si>
+    <t>£45.00</t>
+  </si>
+  <si>
+    <t>£43.50</t>
+  </si>
+  <si>
+    <t>£50.00</t>
+  </si>
+  <si>
+    <t>£54.00</t>
+  </si>
+  <si>
+    <t>£52.50</t>
+  </si>
+  <si>
+    <t>£0.00</t>
+  </si>
+  <si>
+    <t>£22.54</t>
+  </si>
+  <si>
+    <t>£26.28</t>
+  </si>
+  <si>
+    <t>£31.96</t>
+  </si>
+  <si>
+    <t>£36.62</t>
+  </si>
+  <si>
+    <t>£43.70</t>
+  </si>
+  <si>
+    <t>£47.75</t>
+  </si>
+  <si>
+    <t>£48.18</t>
+  </si>
+  <si>
+    <t>£52.76</t>
+  </si>
+  <si>
+    <t>£58.84</t>
+  </si>
+  <si>
+    <t>£61.51</t>
+  </si>
+  <si>
+    <t>£70.54</t>
+  </si>
+  <si>
+    <t>£72.71</t>
+  </si>
+  <si>
+    <t>£83.24</t>
+  </si>
+  <si>
+    <t>£89.03</t>
+  </si>
+  <si>
+    <t>£90.28</t>
+  </si>
+  <si>
+    <t>£77.15</t>
+  </si>
+  <si>
+    <t>£138.11</t>
+  </si>
+  <si>
+    <t>£143.24</t>
+  </si>
+  <si>
+    <t>£161.39</t>
+  </si>
+  <si>
+    <t>£183.47</t>
+  </si>
+  <si>
+    <t>£14.11</t>
+  </si>
+  <si>
+    <t>£17.03</t>
+  </si>
+  <si>
+    <t>£19.93</t>
+  </si>
+  <si>
+    <t>£21.82</t>
+  </si>
+  <si>
+    <t>£26.80</t>
+  </si>
+  <si>
+    <t>£30.17</t>
+  </si>
+  <si>
+    <t>£30.73</t>
+  </si>
+  <si>
+    <t>£34.68</t>
+  </si>
+  <si>
+    <t>£36.08</t>
+  </si>
+  <si>
+    <t>£37.18</t>
+  </si>
+  <si>
+    <t>£45.43</t>
+  </si>
+  <si>
+    <t>£45.86</t>
+  </si>
+  <si>
+    <t>£53.70</t>
+  </si>
+  <si>
+    <t>£53.14</t>
+  </si>
+  <si>
+    <t>£29.11</t>
+  </si>
+  <si>
+    <t>£33.11</t>
+  </si>
+  <si>
+    <t>£37.27</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£66.84</t>
+  </si>
+  <si>
+    <t>£79.89</t>
+  </si>
+  <si>
+    <t>£89.86</t>
+  </si>
+  <si>
+    <t>£93.69</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
+  </si>
+  <si>
+    <t>£303.67</t>
+  </si>
+  <si>
+    <t>£600.15</t>
+  </si>
+  <si>
+    <t>£617.0</t>
+  </si>
+  <si>
+    <t>£795.39</t>
+  </si>
+  <si>
+    <t>£588.75</t>
+  </si>
+  <si>
+    <t>£596.8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,13 +902,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -881,7 +954,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -915,6 +988,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -949,9 +1023,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1124,11 +1199,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1184,7 +1259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1201,46 +1276,46 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
         <v>125</v>
       </c>
-      <c r="I2" t="s">
-        <v>142</v>
-      </c>
       <c r="J2" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="L2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M2" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="N2" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="O2" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="P2" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q2" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="R2" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1257,46 +1332,46 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" t="s">
         <v>126</v>
       </c>
-      <c r="I3" t="s">
-        <v>143</v>
-      </c>
       <c r="J3" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="L3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="N3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="O3" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q3" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
       <c r="R3" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1310,49 +1385,49 @@
         <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" t="s">
         <v>127</v>
       </c>
-      <c r="I4" t="s">
-        <v>144</v>
-      </c>
       <c r="J4" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="L4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="N4" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="O4" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q4" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="R4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1369,46 +1444,46 @@
         <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" t="s">
         <v>128</v>
       </c>
-      <c r="I5" t="s">
-        <v>145</v>
-      </c>
       <c r="J5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" t="s">
+        <v>143</v>
+      </c>
+      <c r="L5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" t="s">
         <v>157</v>
       </c>
-      <c r="K5" t="s">
-        <v>161</v>
-      </c>
-      <c r="L5" t="s">
-        <v>90</v>
-      </c>
-      <c r="M5" t="s">
-        <v>177</v>
-      </c>
       <c r="N5" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="O5" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q5" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="R5" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1425,46 +1500,46 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" t="s">
         <v>129</v>
       </c>
-      <c r="I6" t="s">
-        <v>146</v>
-      </c>
       <c r="J6" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="K6" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="L6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="N6" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="O6" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q6" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="R6" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1481,46 +1556,46 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>208</v>
       </c>
       <c r="G7" t="s">
         <v>72</v>
       </c>
       <c r="H7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" t="s">
         <v>130</v>
       </c>
-      <c r="I7" t="s">
-        <v>147</v>
-      </c>
       <c r="J7" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="L7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="N7" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="O7" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q7" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="R7" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1537,46 +1612,46 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="G8" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" t="s">
         <v>131</v>
       </c>
-      <c r="I8" t="s">
-        <v>148</v>
-      </c>
       <c r="J8" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="K8" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="L8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="N8" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="O8" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="P8" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q8" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="R8" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1593,46 +1668,46 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H9" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" t="s">
         <v>132</v>
       </c>
-      <c r="I9" t="s">
-        <v>149</v>
-      </c>
       <c r="J9" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M9" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="N9" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q9" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="R9" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1649,46 +1724,46 @@
         <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" t="s">
         <v>133</v>
       </c>
-      <c r="I10" t="s">
-        <v>150</v>
-      </c>
       <c r="J10" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N10" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
         <v>74</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q10" t="s">
-        <v>189</v>
+        <v>247</v>
       </c>
       <c r="R10" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1705,46 +1780,46 @@
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>212</v>
       </c>
       <c r="G11" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" t="s">
         <v>134</v>
       </c>
-      <c r="I11" t="s">
-        <v>151</v>
-      </c>
       <c r="J11" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M11" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="N11" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="O11" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="R11" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1758,49 +1833,49 @@
         <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="G12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="J12" t="s">
-        <v>157</v>
+        <v>229</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="O12" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="R12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1817,46 +1892,46 @@
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="I13" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="J13" t="s">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="K13" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="O13" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="R13" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1870,49 +1945,49 @@
         <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="G14" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I14" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="J14" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="K14" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="L14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="O14" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q14" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="R14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1926,49 +2001,49 @@
         <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H15" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I15" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="J15" t="s">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="K15" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" t="s">
+        <v>166</v>
+      </c>
+      <c r="N15" t="s">
+        <v>261</v>
+      </c>
+      <c r="O15" t="s">
+        <v>185</v>
+      </c>
+      <c r="P15" t="s">
         <v>169</v>
       </c>
-      <c r="L15" t="s">
-        <v>90</v>
-      </c>
-      <c r="M15" t="s">
-        <v>186</v>
-      </c>
-      <c r="N15" t="s">
-        <v>200</v>
-      </c>
-      <c r="O15" t="s">
-        <v>218</v>
-      </c>
-      <c r="P15" t="s">
-        <v>189</v>
-      </c>
       <c r="Q15" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="R15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1985,46 +2060,46 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="G16" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="H16" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="J16" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="N16" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="O16" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q16" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="R16" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2032,55 +2107,55 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2091,52 +2166,52 @@
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="K18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="O18" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="P18" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R18" t="s">
-        <v>237</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2147,52 +2222,52 @@
         <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="O19" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2203,52 +2278,52 @@
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2259,52 +2334,52 @@
         <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="K21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2315,52 +2390,52 @@
         <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="K22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2377,46 +2452,46 @@
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" t="s">
         <v>122</v>
       </c>
-      <c r="H23" t="s">
-        <v>139</v>
-      </c>
       <c r="I23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="N23" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="P23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2433,46 +2508,46 @@
         <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
         <v>123</v>
       </c>
-      <c r="H24" t="s">
-        <v>140</v>
-      </c>
       <c r="I24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="L24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="N24" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="O24" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="P24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R24" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2489,43 +2564,43 @@
         <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" t="s">
         <v>124</v>
       </c>
-      <c r="H25" t="s">
-        <v>141</v>
-      </c>
       <c r="I25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="N25" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="O25" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="P25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R25" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
